--- a/CMport_问卷星导入_Day2.xlsx
+++ b/CMport_问卷星导入_Day2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="试题" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,30 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,32 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,524 +413,381 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>题型</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>题干</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>选项A</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>选项B</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>选项C</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>选项D</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>选项E</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>选项F</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>正确答案</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>分值</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>答案解析</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>解析</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>《香港特别行政区基本法》由全国人民代表大会正式通过的年份是？</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>1984年</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1988年</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1990年</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1997年</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》（1990年4月4日由第七届全国人大第三次会议通过）
-基本法于1990年4月4日颁布，1997年7月1日起正式实施，是香港特别行政区的宪制性文件。</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》（1990年4月4日由第七届全国人大第三次会议通过） 基本法于1990年4月4日颁布，1997年7月1日起正式实施，是香港特别行政区的宪制性文件。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1997年7月1日香港回归政权交接仪式在哪里举行？</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>香港会议展览中心</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>香港政府总部</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>九龙礼宾府</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>香港大球场</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>【依据】历史记录
-香港政权交接仪式于1997年7月1日在香港会议展览中心大会堂隆重举行，江泽民主席出席并宣告中国对香港恢复行使主权。</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>【依据】历史记录 香港政权交接仪式于1997年7月1日在香港会议展览中心大会堂隆重举行，江泽民主席出席并宣告中国对香港恢复行使主权。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>香港廉政公署（ICAC）成立于哪一年？</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>1967年</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1974年</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1980年</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1997年</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>【依据】香港廉政公署官方记录（1974年2月15日成立）
-廉政公署于1974年2月15日成立，以独立运作模式推进廉洁施政，回归后依据基本法继续独立运作。</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>【依据】香港廉政公署官方记录（1974年2月15日成立） 廉政公署于1974年2月15日成立，以独立运作模式推进廉洁施政，回归后依据基本法继续独立运作。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>根据《基本法》，香港特别行政区行政长官如何产生？</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>由北京直接委任</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>由香港全体居民直接选举产生</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>由选举委员会选举产生，并报请中央人民政府任命</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>由立法会议员互选产生</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》第四十五条
-基本法第四十五条规定行政长官由当地选举或协商产生，报请中央人民政府任命，现行制度为选举委员会选举产生。</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》第四十五条 基本法第四十五条规定行政长官由当地选举或协商产生，报请中央人民政府任命，现行制度为选举委员会选举产生。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2020年6月30日全国人大常委会通过的涉港重要法律，全称是？</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>《香港维护国家安全条例》</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>《中华人民共和国香港特别行政区维护国家安全法》</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>《全国性国家安全保障法》</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>《反分裂国家法（香港实施细则）》</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《中华人民共和国香港特别行政区维护国家安全法》（2020年6月30日）
-该法于2020年6月30日由全国人大常委会审议通过，同日刊宪实施，有力维护了香港社会稳定。</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>【依据】《中华人民共和国香港特别行政区维护国家安全法》（2020年6月30日） 该法于2020年6月30日由全国人大常委会审议通过，同日刊宪实施，有力维护了香港社会稳定。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>以下哪些人曾担任香港特别行政区行政长官？（多选）</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>以下哪些人曾担任香港特别行政区行政长官？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>董建华</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>曾荫权</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>梁振英</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>林郑月娥</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>【依据】历史记录
-历任行政长官依次为：董建华（1997—2005）、曾荫权（2005—2012）、梁振英（2012—2017）、林郑月娥（2017—2022），现任为李家超（2022年至今）。</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>【依据】历史记录 历任行政长官依次为：董建华（1997—2005）、曾荫权（2005—2012）、梁振英（2012—2017）、林郑月娥（2017—2022），现任为李家超（2022年至今）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>粤港澳大湾区涵盖以下哪些城市/地区？（多选）</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>粤港澳大湾区涵盖以下哪些城市/地区？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>香港、澳门两个特别行政区</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>广州、深圳</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>珠海、佛山、惠州</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>东莞、中山、江门、肇庆</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年）
-大湾区由香港、澳门及广东省9市组成，合称"9+2"；9市分别为广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆。</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年） 大湾区由香港、澳门及广东省9市组成，合称"9+2"；9市分别为广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>多选题</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>《香港特别行政区基本法》涵盖以下哪些方面的内容？（多选）</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>《香港特别行政区基本法》涵盖以下哪些方面的内容？（多选）[多选题]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>香港的政治体制</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>居民的基本权利和义务</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>经济、文化及社会政策</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>对外事务</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》目录（共九章）
-基本法共九章160条，全面规定了香港政治体制、居民权利、经济文化政策及对外事务，是香港的"小宪法"。</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》目录（共九章） 基本法共九章160条，全面规定了香港政治体制、居民权利、经济文化政策及对外事务，是香港的"小宪法"。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>多项填空</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>《香港特别行政区基本法》于{1990}年{4}月{4}日正式颁布，并于1997年7月1日起实施，是香港特别行政区的宪制性文件。</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>1990;4;4</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>【依据】《香港特别行政区基本法》颁布日期
-基本法的颁布标志着"一国两制"在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>【依据】《香港特别行政区基本法》颁布日期 基本法的颁布标志着"一国两制"在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>填空题</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1997年香港回归政权交接仪式上，代表中国政府郑重宣告对香港恢复行使主权的时任中华人民共和国主席是{江泽民}。</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>江泽民</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>【依据】历史记录
-时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>【依据】历史记录 时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。</t>
         </is>
       </c>
     </row>

--- a/CMport_问卷星导入_Day2.xlsx
+++ b/CMport_问卷星导入_Day2.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》（1990年4月4日由第七届全国人大第三次会议通过） 基本法于1990年4月4日颁布，1997年7月1日起正式实施，是香港特别行政区的宪制性文件。</t>
+          <t>依据：《香港特别行政区基本法》（1990年4月4日由第七届全国人大第三次会议通过）。基本法于1990年4月4日颁布，1997年7月1日起正式实施，是香港特别行政区的宪制性文件。</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>【依据】历史记录 香港政权交接仪式于1997年7月1日在香港会议展览中心大会堂隆重举行，江泽民主席出席并宣告中国对香港恢复行使主权。</t>
+          <t>依据：历史记录。香港政权交接仪式于1997年7月1日在香港会议展览中心大会堂隆重举行，江泽民主席出席并宣告中国对香港恢复行使主权。</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>【依据】香港廉政公署官方记录（1974年2月15日成立） 廉政公署于1974年2月15日成立，以独立运作模式推进廉洁施政，回归后依据基本法继续独立运作。</t>
+          <t>依据：香港廉政公署官方记录（1974年2月15日成立）。廉政公署于1974年2月15日成立，以独立运作模式推进廉洁施政，回归后依据基本法继续独立运作。</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》第四十五条 基本法第四十五条规定行政长官由当地选举或协商产生，报请中央人民政府任命，现行制度为选举委员会选举产生。</t>
+          <t>依据：《香港特别行政区基本法》第四十五条。基本法第四十五条规定行政长官由当地选举或协商产生，报请中央人民政府任命，现行制度为选举委员会选举产生。</t>
         </is>
       </c>
     </row>
@@ -634,14 +634,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>【依据】《中华人民共和国香港特别行政区维护国家安全法》（2020年6月30日） 该法于2020年6月30日由全国人大常委会审议通过，同日刊宪实施，有力维护了香港社会稳定。</t>
+          <t>依据：《中华人民共和国香港特别行政区维护国家安全法》（2020年6月30日）。该法于2020年6月30日由全国人大常委会审议通过，同日刊宪实施，有力维护了香港社会稳定。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>以下哪些人曾担任香港特别行政区行政长官？（多选）[多选题]</t>
+          <t>以下哪些人曾担任香港特别行政区行政长官？(ABCD)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>【依据】历史记录 历任行政长官依次为：董建华（1997—2005）、曾荫权（2005—2012）、梁振英（2012—2017）、林郑月娥（2017—2022），现任为李家超（2022年至今）。</t>
+          <t>依据：历史记录。历任行政长官依次为：董建华（1997—2005）、曾荫权（2005—2012）、梁振英（2012—2017）、林郑月娥（2017—2022），现任为李家超（2022年至今）。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>粤港澳大湾区涵盖以下哪些城市/地区？（多选）[多选题]</t>
+          <t>粤港澳大湾区涵盖以下哪些城市/地区？(ABCD)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>【依据】《粤港澳大湾区发展规划纲要》（2019年） 大湾区由香港、澳门及广东省9市组成，合称"9+2"；9市分别为广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆。</t>
+          <t>依据：《粤港澳大湾区发展规划纲要》（2019年）。大湾区由香港、澳门及广东省9市组成，合称9+2；9市分别为广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>《香港特别行政区基本法》涵盖以下哪些方面的内容？（多选）[多选题]</t>
+          <t>《香港特别行政区基本法》涵盖以下哪些方面的内容？(ABCD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》目录（共九章） 基本法共九章160条，全面规定了香港政治体制、居民权利、经济文化政策及对外事务，是香港的"小宪法"。</t>
+          <t>依据：《香港特别行政区基本法》目录（共九章）。基本法共九章160条，全面规定了香港政治体制、居民权利、经济文化政策及对外事务，是香港的小宪法。</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>【依据】《香港特别行政区基本法》颁布日期 基本法的颁布标志着"一国两制"在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。</t>
+          <t>依据：《香港特别行政区基本法》颁布日期。基本法的颁布标志着一国两制在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>【依据】历史记录 时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。</t>
+          <t>依据：历史记录。时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。</t>
         </is>
       </c>
     </row>

--- a/CMport_问卷星导入_Day2.xlsx
+++ b/CMport_问卷星导入_Day2.xlsx
@@ -413,8 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -422,372 +425,74 @@
           <t>题干</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>选项A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>选项B</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>选项C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>选项D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>正确答案</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>解析</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>《香港特别行政区基本法》由全国人民代表大会正式通过的年份是？</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1984年</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1988年</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1990年</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1997年</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》（1990年4月4日由第七届全国人大第三次会议通过）。基本法于1990年4月4日颁布，1997年7月1日起正式实施，是香港特别行政区的宪制性文件。</t>
+          <t>1. 《香港特别行政区基本法》由全国人民代表大会正式通过的年份是？&lt;br/&gt;&lt;br/&gt;A. 1984年&lt;br/&gt;B. 1988年&lt;br/&gt;C. 1990年&lt;br/&gt;D. 1997年&lt;br/&gt;&lt;br/&gt;答案：C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1997年7月1日香港回归政权交接仪式在哪里举行？</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>香港会议展览中心</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>香港政府总部</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>九龙礼宾府</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>香港大球场</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>依据：历史记录。香港政权交接仪式于1997年7月1日在香港会议展览中心大会堂隆重举行，江泽民主席出席并宣告中国对香港恢复行使主权。</t>
+          <t>2. 1997年7月1日香港回归政权交接仪式在哪里举行？&lt;br/&gt;&lt;br/&gt;A. 香港会议展览中心&lt;br/&gt;B. 香港政府总部&lt;br/&gt;C. 九龙礼宾府&lt;br/&gt;D. 香港大球场&lt;br/&gt;&lt;br/&gt;答案：A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>香港廉政公署（ICAC）成立于哪一年？</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1967年</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1974年</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1980年</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1997年</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>依据：香港廉政公署官方记录（1974年2月15日成立）。廉政公署于1974年2月15日成立，以独立运作模式推进廉洁施政，回归后依据基本法继续独立运作。</t>
+          <t>3. 香港廉政公署（ICAC）成立于哪一年？&lt;br/&gt;&lt;br/&gt;A. 1967年&lt;br/&gt;B. 1974年&lt;br/&gt;C. 1980年&lt;br/&gt;D. 1997年&lt;br/&gt;&lt;br/&gt;答案：B</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>根据《基本法》，香港特别行政区行政长官如何产生？</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>由北京直接委任</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>由香港全体居民直接选举产生</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>由选举委员会选举产生，并报请中央人民政府任命</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>由立法会议员互选产生</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》第四十五条。基本法第四十五条规定行政长官由当地选举或协商产生，报请中央人民政府任命，现行制度为选举委员会选举产生。</t>
+          <t>4. 根据《基本法》，香港特别行政区行政长官如何产生？&lt;br/&gt;&lt;br/&gt;A. 由北京直接委任&lt;br/&gt;B. 由香港全体居民直接选举产生&lt;br/&gt;C. 由选举委员会选举产生，并报请中央人民政府任命&lt;br/&gt;D. 由立法会议员互选产生&lt;br/&gt;&lt;br/&gt;答案：C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020年6月30日全国人大常委会通过的涉港重要法律，全称是？</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>《香港维护国家安全条例》</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>《中华人民共和国香港特别行政区维护国家安全法》</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>《全国性国家安全保障法》</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>《反分裂国家法（香港实施细则）》</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>依据：《中华人民共和国香港特别行政区维护国家安全法》（2020年6月30日）。该法于2020年6月30日由全国人大常委会审议通过，同日刊宪实施，有力维护了香港社会稳定。</t>
+          <t>5. 2020年6月30日全国人大常委会通过的涉港重要法律，全称是？&lt;br/&gt;&lt;br/&gt;A. 《香港维护国家安全条例》&lt;br/&gt;B. 《中华人民共和国香港特别行政区维护国家安全法》&lt;br/&gt;C. 《全国性国家安全保障法》&lt;br/&gt;D. 《反分裂国家法（香港实施细则）》&lt;br/&gt;&lt;br/&gt;答案：B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>以下哪些人曾担任香港特别行政区行政长官？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>董建华</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>曾荫权</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>梁振英</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>林郑月娥</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>依据：历史记录。历任行政长官依次为：董建华（1997—2005）、曾荫权（2005—2012）、梁振英（2012—2017）、林郑月娥（2017—2022），现任为李家超（2022年至今）。</t>
+          <t>6. 以下哪些人曾担任香港特别行政区行政长官（ ）&lt;br/&gt;&lt;br/&gt;A. 董建华&lt;br/&gt;B. 曾荫权&lt;br/&gt;C. 梁振英&lt;br/&gt;D. 林郑月娥&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>粤港澳大湾区涵盖以下哪些城市/地区？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>香港、澳门两个特别行政区</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>广州、深圳</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>珠海、佛山、惠州</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>东莞、中山、江门、肇庆</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>依据：《粤港澳大湾区发展规划纲要》（2019年）。大湾区由香港、澳门及广东省9市组成，合称9+2；9市分别为广州、深圳、珠海、佛山、惠州、东莞、中山、江门、肇庆。</t>
+          <t>7. 粤港澳大湾区涵盖以下哪些城市/地区（ ）&lt;br/&gt;&lt;br/&gt;A. 香港、澳门两个特别行政区&lt;br/&gt;B. 广州、深圳&lt;br/&gt;C. 珠海、佛山、惠州&lt;br/&gt;D. 东莞、中山、江门、肇庆&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>《香港特别行政区基本法》涵盖以下哪些方面的内容？(ABCD)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>香港的政治体制</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>居民的基本权利和义务</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>经济、文化及社会政策</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>对外事务</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》目录（共九章）。基本法共九章160条，全面规定了香港政治体制、居民权利、经济文化政策及对外事务，是香港的小宪法。</t>
+          <t>8. 《香港特别行政区基本法》涵盖以下哪些方面的内容（ ）&lt;br/&gt;&lt;br/&gt;A. 香港的政治体制&lt;br/&gt;B. 居民的基本权利和义务&lt;br/&gt;C. 经济、文化及社会政策&lt;br/&gt;D. 对外事务&lt;br/&gt;&lt;br/&gt;答案：ABCD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>《香港特别行政区基本法》于{1990}年{4}月{4}日正式颁布，并于1997年7月1日起实施，是香港特别行政区的宪制性文件。</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1990;4;4</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>依据：《香港特别行政区基本法》颁布日期。基本法的颁布标志着一国两制在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。</t>
+          <t>9. 《香港特别行政区基本法》于____年____月____日正式颁布，并于1997年7月1日起实施，是香港特别行政区的宪制性文件。&lt;br/&gt;&lt;br/&gt;答案：1990；4；4&lt;br/&gt;&lt;br/&gt;解析：依据：《香港特别行政区基本法》颁布日期。基本法的颁布标志着一国两制在法律层面的制度化，为香港回归后的平稳过渡提供了根本保障。&lt;br/&gt;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1997年香港回归政权交接仪式上，代表中国政府郑重宣告对香港恢复行使主权的时任中华人民共和国主席是{江泽民}。</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>江泽民</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>依据：历史记录。时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。</t>
+          <t>10. 1997年香港回归政权交接仪式上，代表中国政府郑重宣告对香港恢复行使主权的时任中华人民共和国主席是____。&lt;br/&gt;&lt;br/&gt;答案：江泽民&lt;br/&gt;&lt;br/&gt;解析：依据：历史记录。时任国家主席江泽民出席香港回归政权交接仪式，代表中国政府宣告中国对香港正式恢复行使主权，具有重大历史意义。&lt;br/&gt;</t>
         </is>
       </c>
     </row>
